--- a/Employee_Reports_wi52/Conrado DE Guzman Vineza Q0428.xlsx
+++ b/Employee_Reports_wi52/Conrado DE Guzman Vineza Q0428.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1305,11 +1305,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1354,11 +1354,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1391,11 +1391,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-168</v>
+        <v>-176</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1440,11 +1440,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1489,11 +1489,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1538,11 +1538,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1587,11 +1587,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1624,11 +1624,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1661,11 +1661,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1698,11 +1698,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1747,11 +1747,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1775,20 +1775,20 @@
       <c r="E29" s="3" t="inlineStr"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>06-Jul-2025</t>
+          <t>24-Aug-2026</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>06-Jul-2027</t>
+          <t>23-Aug-2028</t>
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>320</v>
+        <v>726</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7905</v>
+        <v>7897</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7900</v>
+        <v>7892</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7922</v>
+        <v>7914</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7900</v>
+        <v>7892</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7944</v>
+        <v>7936</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7944</v>
+        <v>7936</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2658,7 +2658,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7965</v>
+        <v>7957</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7929</v>
+        <v>7921</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7965</v>
+        <v>7957</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7965</v>
+        <v>7957</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7965</v>
+        <v>7957</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7956</v>
+        <v>7948</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
